--- a/docs/prilohy/Soupis spojovacího materiálu.xlsx
+++ b/docs/prilohy/Soupis spojovacího materiálu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\PRODUCTION\Výrobní manuál\Projekty\conway-2027\docs\prilohy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.11\Hartje_Sdílené\PRODUCTION\Výrobní manuál\Projekty\conway-2027\docs\prilohy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B23775-8D3B-4F22-B6E9-62BF8306EFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51F1537-FD61-40A8-93AA-3F2E423E7431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{754624A3-F4C5-42E0-9369-5418F4FB9EC3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>M5x8</t>
   </si>
@@ -99,13 +99,46 @@
   </si>
   <si>
     <t>M6x14</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Počet ks</t>
+  </si>
+  <si>
+    <t>C 4.0</t>
+  </si>
+  <si>
+    <t>C 1.0 N</t>
+  </si>
+  <si>
+    <t>C 1.0 B</t>
+  </si>
+  <si>
+    <t>C 2.0 B</t>
+  </si>
+  <si>
+    <t>C 4.0 B</t>
+  </si>
+  <si>
+    <t>S 2.0</t>
+  </si>
+  <si>
+    <t>S 3.0</t>
+  </si>
+  <si>
+    <t>odhad spojováku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S 2.0 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,16 +147,49 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -237,6 +303,152 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -244,7 +456,9 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -253,7 +467,9 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -262,100 +478,6 @@
         <color indexed="64"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -367,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -387,58 +509,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -775,35 +928,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C755BE-C58B-48E6-8B2B-9CA33BDF40C1}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="9.140625" style="1"/>
+    <col min="5" max="5" width="12.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="20"/>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="25"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -812,305 +967,613 @@
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="26">
+        <v>2027</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="7">
         <v>6</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10">
+      <c r="D3" s="7">
         <v>9</v>
       </c>
-      <c r="G3" s="11">
+      <c r="E3" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="F3" s="27">
+        <f>SUM(G3:N3)</f>
+        <v>97500</v>
+      </c>
+      <c r="G3">
+        <f>$B$17*C3</f>
+        <v>9000</v>
+      </c>
+      <c r="H3">
+        <f>$B$18*C3</f>
+        <v>15000</v>
+      </c>
+      <c r="I3">
+        <f>$B$19*C3</f>
+        <v>15000</v>
+      </c>
+      <c r="J3">
+        <f>$B$20*C3</f>
+        <v>9600</v>
+      </c>
+      <c r="K3">
+        <f>$B$23*C3</f>
+        <v>18600</v>
+      </c>
+      <c r="L3">
+        <f>$B$24*C3</f>
+        <v>10800</v>
+      </c>
+      <c r="M3">
+        <f>$B$25*E3</f>
+        <v>13000</v>
+      </c>
+      <c r="N3">
+        <f>$B$26*E3</f>
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="14">
         <v>6</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" s="14"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="27">
+        <f t="shared" ref="F4:F13" si="0">SUM(G4:N4)</f>
+        <v>78000</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4:G13" si="1">$B$17*C4</f>
+        <v>9000</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H13" si="2">$B$18*C4</f>
+        <v>15000</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I13" si="3">$B$19*C4</f>
+        <v>15000</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J13" si="4">$B$20*C4</f>
+        <v>9600</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ref="K4:K13" si="5">$B$23*C4</f>
+        <v>18600</v>
+      </c>
+      <c r="L4">
+        <f t="shared" ref="L4:L13" si="6">$B$24*C4</f>
+        <v>10800</v>
+      </c>
+      <c r="M4">
+        <f t="shared" ref="M4:M13" si="7">$B$25*E4</f>
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f t="shared" ref="N4:N13" si="8">$B$26*E4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="1">
         <v>2</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15">
+      <c r="D5" s="1">
         <v>2</v>
       </c>
-      <c r="G5" s="16">
+      <c r="E5" s="12">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="F5" s="27">
+        <f t="shared" si="0"/>
+        <v>29000</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="3"/>
+        <v>5000</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="4"/>
+        <v>3200</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="5"/>
+        <v>6200</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="6"/>
+        <v>3600</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="7"/>
+        <v>2000</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="8"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="17">
         <v>1</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="23"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="D6" s="17"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="27">
+        <f t="shared" si="0"/>
+        <v>13000</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="2"/>
+        <v>2500</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="3"/>
+        <v>2500</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="4"/>
+        <v>1600</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="5"/>
+        <v>3100</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="6"/>
+        <v>1800</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="16"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+      <c r="E7" s="12"/>
+      <c r="F7" s="27">
+        <f t="shared" si="0"/>
+        <v>26000</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="3"/>
+        <v>5000</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="4"/>
+        <v>3200</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="5"/>
+        <v>6200</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="6"/>
+        <v>3600</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="17">
         <v>2</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="23"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="27">
+        <f t="shared" si="0"/>
+        <v>26000</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="3"/>
+        <v>5000</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="4"/>
+        <v>3200</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="5"/>
+        <v>6200</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="6"/>
+        <v>3600</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15">
+      <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="16">
+      <c r="E9" s="12">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
+      <c r="F9" s="27">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="7"/>
+        <v>1000</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="8"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>2</v>
+      </c>
       <c r="B10" s="21"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="23"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="23"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="23"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="23"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="23"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="6"/>
+      <c r="F10"/>
+      <c r="G10"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="33"/>
+      <c r="B12" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="35">
+        <v>9</v>
+      </c>
+      <c r="D12" s="36">
+        <v>9</v>
+      </c>
+      <c r="E12" s="37">
+        <v>13</v>
+      </c>
+      <c r="F12" s="27">
+        <f t="shared" si="0"/>
+        <v>136500</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>13500</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>22500</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="3"/>
+        <v>22500</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="4"/>
+        <v>14400</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="5"/>
+        <v>27900</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="6"/>
+        <v>16200</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="7"/>
+        <v>13000</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="8"/>
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+      <c r="B13" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1</v>
+      </c>
+      <c r="D13" s="10">
         <v>2</v>
       </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="9">
-        <v>9</v>
-      </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10">
-        <v>9</v>
-      </c>
-      <c r="G25" s="11">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="12">
+      <c r="E13" s="11">
+        <v>2</v>
+      </c>
+      <c r="F13" s="27">
+        <f t="shared" si="0"/>
+        <v>16000</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="2"/>
+        <v>2500</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="3"/>
+        <v>2500</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="4"/>
+        <v>1600</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="5"/>
+        <v>3100</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="6"/>
+        <v>1800</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="7"/>
+        <v>2000</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="8"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13">
-        <v>2</v>
-      </c>
-      <c r="G26" s="14">
-        <v>2</v>
+      <c r="B17" s="23">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="23">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="23">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="23">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="23">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="23">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="23">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="23">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="23">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27"/>
+      <c r="B27" s="24">
+        <f>SUM(B17:B26)</f>
+        <v>14800</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A10:B10"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>